--- a/outputs/254-34.xlsx
+++ b/outputs/254-34.xlsx
@@ -118,20 +118,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -390,89 +394,89 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.3671875" defaultRowHeight="21" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="n">
+      <c r="A1" s="2" t="n">
         <v>22704</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>345510</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>994110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>1238917</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>30424</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>564077.969</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>406153</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>60073</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>436880</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>158419</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>277936.0475</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>293976</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>827362</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>342830</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>146354</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>1146945</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>230626</v>
       </c>
     </row>
@@ -496,82 +500,82 @@
   <sheetFormatPr defaultColWidth="8.3671875" defaultRowHeight="21" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="n">
+      <c r="A1" s="4" t="n">
         <v>22704</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>345510</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>1238917</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>30424</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>564077.969</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>406153</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>60073</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>436880</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>158419</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>277936.0475</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>293976</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>827362</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>342830</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>146354</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>1146945</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>230626</v>
       </c>
     </row>
